--- a/salidas/empresas/AMAT.xlsx
+++ b/salidas/empresas/AMAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.82302379608154</v>
+        <v>13.82302474975586</v>
       </c>
       <c r="C2" t="n">
         <v>19.04999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31343364715576</v>
+        <v>13.31342887878418</v>
       </c>
       <c r="C3" t="n">
         <v>18.31999969482422</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.72478866577148</v>
+        <v>12.72479343414307</v>
       </c>
       <c r="C4" t="n">
         <v>17.51000022888184</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.86435413360596</v>
+        <v>11.86435317993164</v>
       </c>
       <c r="C7" t="n">
         <v>16.28000068664551</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.48539352416992</v>
+        <v>11.4853982925415</v>
       </c>
       <c r="C8" t="n">
         <v>15.76000022888184</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.35630798339844</v>
+        <v>12.35631275177002</v>
       </c>
       <c r="C9" t="n">
         <v>16.89999961853027</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.96315765380859</v>
+        <v>12.96316051483154</v>
       </c>
       <c r="C10" t="n">
         <v>17.72999954223633</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.71456527709961</v>
+        <v>12.71457290649414</v>
       </c>
       <c r="C11" t="n">
         <v>17.38999938964844</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>13.20435047149658</v>
+        <v>13.20434856414795</v>
       </c>
       <c r="C12" t="n">
         <v>18.01000022888184</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52694702148438</v>
+        <v>13.52694797515869</v>
       </c>
       <c r="C13" t="n">
         <v>18.45000076293945</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.99906635284424</v>
+        <v>12.99906444549561</v>
       </c>
       <c r="C14" t="n">
         <v>17.72999954223633</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.65308570861816</v>
+        <v>13.65308475494385</v>
       </c>
       <c r="C15" t="n">
         <v>18.56999969482422</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.46927738189697</v>
+        <v>13.46927452087402</v>
       </c>
       <c r="C16" t="n">
         <v>18.31999969482422</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.13098049163818</v>
+        <v>14.13097858428955</v>
       </c>
       <c r="C17" t="n">
         <v>19.21999931335449</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.08401489257812</v>
+        <v>14.08401298522949</v>
       </c>
       <c r="C18" t="n">
         <v>19.10000038146973</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.65179538726807</v>
+        <v>14.65179920196533</v>
       </c>
       <c r="C19" t="n">
         <v>19.8700008392334</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.25191879272461</v>
+        <v>16.25192070007324</v>
       </c>
       <c r="C20" t="n">
         <v>22.04000091552734</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.79408740997314</v>
+        <v>15.79409027099609</v>
       </c>
       <c r="C21" t="n">
         <v>21.36000061035156</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.30606937408447</v>
+        <v>15.30607414245605</v>
       </c>
       <c r="C22" t="n">
         <v>20.70000076293945</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.35961151123047</v>
+        <v>14.35960578918457</v>
       </c>
       <c r="C23" t="n">
         <v>19.42000007629395</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>13.96912288665771</v>
+        <v>13.96912574768066</v>
       </c>
       <c r="C24" t="n">
         <v>18.82999992370605</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>13.17534065246582</v>
+        <v>13.17533302307129</v>
       </c>
       <c r="C25" t="n">
         <v>17.76000022888184</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>13.29403495788574</v>
+        <v>13.29403209686279</v>
       </c>
       <c r="C26" t="n">
         <v>17.92000007629395</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.26765441894531</v>
+        <v>14.26764869689941</v>
       </c>
       <c r="C27" t="n">
         <v>19.17000007629395</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>14.52070236206055</v>
+        <v>14.52070140838623</v>
       </c>
       <c r="C28" t="n">
         <v>19.51000022888184</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.88806915283203</v>
+        <v>13.88807201385498</v>
       </c>
       <c r="C29" t="n">
         <v>18.65999984741211</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.78864288330078</v>
+        <v>14.78864574432373</v>
       </c>
       <c r="C30" t="n">
         <v>19.80999946594238</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.25114727020264</v>
+        <v>14.25114631652832</v>
       </c>
       <c r="C31" t="n">
         <v>19.09000015258789</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>12.92979621887207</v>
+        <v>12.92979907989502</v>
       </c>
       <c r="C32" t="n">
         <v>17.31999969482422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.42119407653809</v>
+        <v>13.42119121551514</v>
       </c>
       <c r="C33" t="n">
         <v>17.92000007629395</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>11.33161926269531</v>
+        <v>11.33162117004395</v>
       </c>
       <c r="C34" t="n">
         <v>15.13000011444092</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>9.668951988220215</v>
+        <v>9.668949127197266</v>
       </c>
       <c r="C35" t="n">
         <v>12.90999984741211</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.213245868682861</v>
+        <v>7.213242530822754</v>
       </c>
       <c r="C36" t="n">
         <v>9.579999923706055</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.627366065979004</v>
+        <v>7.627368450164795</v>
       </c>
       <c r="C37" t="n">
         <v>10.13000011444092</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.055127143859863</v>
+        <v>7.055124759674072</v>
       </c>
       <c r="C38" t="n">
         <v>9.369999885559082</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.975688934326172</v>
+        <v>6.975687026977539</v>
       </c>
       <c r="C39" t="n">
         <v>9.210000038146973</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.142091751098633</v>
+        <v>8.142095565795898</v>
       </c>
       <c r="C40" t="n">
         <v>10.75</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.247901916503906</v>
+        <v>9.247896194458008</v>
       </c>
       <c r="C41" t="n">
         <v>12.21000003814697</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.572029113769531</v>
+        <v>8.572028160095215</v>
       </c>
       <c r="C42" t="n">
         <v>11.26000022888184</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.381707191467285</v>
+        <v>8.381702423095703</v>
       </c>
       <c r="C43" t="n">
         <v>11.01000022888184</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.07838153839111</v>
+        <v>10.0783805847168</v>
       </c>
       <c r="C45" t="n">
         <v>13.18000030517578</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.23131084442139</v>
+        <v>10.23131275177002</v>
       </c>
       <c r="C46" t="n">
         <v>13.38000011444092</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.329002380371094</v>
+        <v>9.32900333404541</v>
       </c>
       <c r="C47" t="n">
         <v>12.19999980926514</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>9.458888053894043</v>
+        <v>9.458884239196777</v>
       </c>
       <c r="C48" t="n">
         <v>12.3100004196167</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>10.7113561630249</v>
+        <v>10.7113618850708</v>
       </c>
       <c r="C49" t="n">
         <v>13.9399995803833</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.358993530273438</v>
+        <v>9.358994483947754</v>
       </c>
       <c r="C50" t="n">
         <v>12.18000030517578</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>9.450455665588379</v>
+        <v>9.450457572937012</v>
       </c>
       <c r="C51" t="n">
         <v>12.23999977111816</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.40013980865479</v>
+        <v>10.40013599395752</v>
       </c>
       <c r="C52" t="n">
         <v>13.47000026702881</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>10.63948917388916</v>
+        <v>10.63949012756348</v>
       </c>
       <c r="C53" t="n">
         <v>13.77999973297119</v>
@@ -1518,7 +1530,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>9.331954002380371</v>
+        <v>9.331957817077637</v>
       </c>
       <c r="C55" t="n">
         <v>12.02000045776367</v>
@@ -1568,7 +1580,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.102084159851074</v>
+        <v>8.102083206176758</v>
       </c>
       <c r="C57" t="n">
         <v>10.36999988555908</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.125587463378906</v>
+        <v>9.125585556030273</v>
       </c>
       <c r="C58" t="n">
         <v>11.68000030517578</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.649059295654297</v>
+        <v>9.64906120300293</v>
       </c>
       <c r="C59" t="n">
         <v>12.35000038146973</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.766120910644531</v>
+        <v>9.76612377166748</v>
       </c>
       <c r="C60" t="n">
         <v>12.43000030517578</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>11.0389404296875</v>
+        <v>11.03893661499023</v>
       </c>
       <c r="C61" t="n">
         <v>14.05000019073486</v>
@@ -1722,11 +1734,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>12.32746982574463</v>
+        <v>12.32746887207031</v>
       </c>
       <c r="C62" t="n">
         <v>15.6899995803833</v>
@@ -1751,11 +1763,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.96518039703369</v>
+        <v>12.96518325805664</v>
       </c>
       <c r="C63" t="n">
         <v>16.43000030517578</v>
@@ -1780,11 +1792,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>12.3259973526001</v>
+        <v>12.32599830627441</v>
       </c>
       <c r="C64" t="n">
         <v>15.61999988555908</v>
@@ -1809,11 +1821,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>12.38123512268066</v>
+        <v>12.38123416900635</v>
       </c>
       <c r="C65" t="n">
         <v>15.6899995803833</v>
@@ -1838,11 +1850,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.93817615509033</v>
+        <v>10.93817806243896</v>
       </c>
       <c r="C66" t="n">
         <v>13.77999973297119</v>
@@ -1867,11 +1879,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.32697200775146</v>
+        <v>10.32697582244873</v>
       </c>
       <c r="C67" t="n">
         <v>13.01000022888184</v>
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>9.779266357421875</v>
+        <v>9.77927303314209</v>
       </c>
       <c r="C68" t="n">
         <v>12.31999969482422</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>9.050965309143066</v>
+        <v>9.050967216491699</v>
       </c>
       <c r="C69" t="n">
         <v>11.31999969482422</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.283390998840332</v>
+        <v>8.283390045166016</v>
       </c>
       <c r="C70" t="n">
         <v>10.35999965667725</v>
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2012,7 +2024,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.624674797058105</v>
+        <v>8.624679565429688</v>
       </c>
       <c r="C73" t="n">
         <v>10.71000003814697</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>9.88898754119873</v>
+        <v>9.888984680175781</v>
       </c>
       <c r="C74" t="n">
         <v>12.27999973297119</v>
@@ -2099,11 +2111,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.925958633422852</v>
+        <v>9.92595386505127</v>
       </c>
       <c r="C75" t="n">
         <v>12.25</v>
@@ -2128,11 +2140,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.08801460266113</v>
+        <v>10.08800983428955</v>
       </c>
       <c r="C76" t="n">
         <v>12.44999980926514</v>
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>9.715285301208496</v>
+        <v>9.71528148651123</v>
       </c>
       <c r="C77" t="n">
         <v>11.98999977111816</v>
@@ -2186,11 +2198,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>8.441487312316895</v>
+        <v>8.441483497619629</v>
       </c>
       <c r="C78" t="n">
         <v>10.32999992370605</v>
@@ -2215,11 +2227,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.356728553771973</v>
+        <v>9.356727600097656</v>
       </c>
       <c r="C79" t="n">
         <v>11.44999980926514</v>
@@ -2244,11 +2256,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>8.899105072021484</v>
+        <v>8.899106979370117</v>
       </c>
       <c r="C80" t="n">
         <v>10.89000034332275</v>
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>9.625223159790039</v>
+        <v>9.625221252441406</v>
       </c>
       <c r="C81" t="n">
         <v>11.6899995803833</v>
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>9.197064399719238</v>
+        <v>9.197068214416504</v>
       </c>
       <c r="C82" t="n">
         <v>11.17000007629395</v>
@@ -2331,11 +2343,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>8.72774600982666</v>
+        <v>8.727743148803711</v>
       </c>
       <c r="C83" t="n">
         <v>10.60000038146973</v>
@@ -2360,11 +2372,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>8.913825035095215</v>
+        <v>8.913824081420898</v>
       </c>
       <c r="C84" t="n">
         <v>10.72999954223633</v>
@@ -2389,7 +2401,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2418,11 +2430,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>10.7248363494873</v>
+        <v>10.72483539581299</v>
       </c>
       <c r="C86" t="n">
         <v>12.90999984741211</v>
@@ -2447,11 +2459,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>11.46370220184326</v>
+        <v>11.46370697021484</v>
       </c>
       <c r="C87" t="n">
         <v>13.71000003814697</v>
@@ -2476,11 +2488,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>11.27138710021973</v>
+        <v>11.27138423919678</v>
       </c>
       <c r="C88" t="n">
         <v>13.47999954223633</v>
@@ -2505,11 +2517,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>12.13262748718262</v>
+        <v>12.13262557983398</v>
       </c>
       <c r="C89" t="n">
         <v>14.51000022888184</v>
@@ -2534,11 +2546,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>12.79539012908936</v>
+        <v>12.7953929901123</v>
       </c>
       <c r="C90" t="n">
         <v>15.19999980926514</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>12.55968952178955</v>
+        <v>12.55969047546387</v>
       </c>
       <c r="C91" t="n">
         <v>14.92000007629395</v>
@@ -2588,11 +2600,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.7382116317749</v>
+        <v>13.73821353912354</v>
       </c>
       <c r="C92" t="n">
         <v>16.31999969482422</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>12.71723556518555</v>
+        <v>12.7172327041626</v>
       </c>
       <c r="C93" t="n">
         <v>15.01000022888184</v>
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.85230541229248</v>
+        <v>14.85230731964111</v>
       </c>
       <c r="C94" t="n">
         <v>17.53000068664551</v>
@@ -2669,11 +2681,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>15.13189888000488</v>
+        <v>15.13189601898193</v>
       </c>
       <c r="C95" t="n">
         <v>17.86000061035156</v>
@@ -2696,11 +2708,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>14.74447536468506</v>
+        <v>14.74447631835938</v>
       </c>
       <c r="C96" t="n">
         <v>17.29999923706055</v>
@@ -2723,11 +2735,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>15.0683422088623</v>
+        <v>15.06834316253662</v>
       </c>
       <c r="C97" t="n">
         <v>17.68000030517578</v>
@@ -2752,11 +2764,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>14.3353796005249</v>
+        <v>14.3353853225708</v>
       </c>
       <c r="C98" t="n">
         <v>16.81999969482422</v>
@@ -2781,11 +2793,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.2453556060791</v>
+        <v>16.24535369873047</v>
       </c>
       <c r="C99" t="n">
         <v>18.95999908447266</v>
@@ -2810,11 +2822,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.49630928039551</v>
+        <v>17.49631881713867</v>
       </c>
       <c r="C100" t="n">
         <v>20.42000007629395</v>
@@ -2839,11 +2851,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>16.33103942871094</v>
+        <v>16.33103561401367</v>
       </c>
       <c r="C101" t="n">
         <v>19.05999946594238</v>
@@ -2868,11 +2880,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.38564872741699</v>
+        <v>17.38566017150879</v>
       </c>
       <c r="C102" t="n">
         <v>20.19000053405762</v>
@@ -2897,7 +2909,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2926,11 +2938,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.04870223999023</v>
+        <v>18.0487003326416</v>
       </c>
       <c r="C104" t="n">
         <v>20.95999908447266</v>
@@ -2955,11 +2967,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.99052810668945</v>
+        <v>19.99053382873535</v>
       </c>
       <c r="C105" t="n">
         <v>23.11000061035156</v>
@@ -2984,11 +2996,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.69301223754883</v>
+        <v>18.6930103302002</v>
       </c>
       <c r="C106" t="n">
         <v>21.61000061035156</v>
@@ -3013,11 +3025,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>19.10821342468262</v>
+        <v>19.10821533203125</v>
       </c>
       <c r="C107" t="n">
         <v>22.09000015258789</v>
@@ -3042,11 +3054,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>20.8966007232666</v>
+        <v>20.8966121673584</v>
       </c>
       <c r="C108" t="n">
         <v>24.04999923706055</v>
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>21.65252685546875</v>
+        <v>21.65253448486328</v>
       </c>
       <c r="C109" t="n">
         <v>24.92000007629395</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.84526443481445</v>
+        <v>19.84525680541992</v>
       </c>
       <c r="C110" t="n">
         <v>22.84000015258789</v>
@@ -3129,11 +3141,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>21.85602188110352</v>
+        <v>21.85601997375488</v>
       </c>
       <c r="C111" t="n">
         <v>25.04999923706055</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.68351173400879</v>
+        <v>19.68350410461426</v>
       </c>
       <c r="C112" t="n">
         <v>22.55999946594238</v>
@@ -3187,11 +3199,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>17.26669311523438</v>
+        <v>17.26669120788574</v>
       </c>
       <c r="C113" t="n">
         <v>19.79000091552734</v>
@@ -3216,11 +3228,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>17.6507682800293</v>
+        <v>17.65076637268066</v>
       </c>
       <c r="C114" t="n">
         <v>20.1299991607666</v>
@@ -3245,11 +3257,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>16.85284042358398</v>
+        <v>16.85283851623535</v>
       </c>
       <c r="C115" t="n">
         <v>19.21999931335449</v>
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>15.22192668914795</v>
+        <v>15.22192478179932</v>
       </c>
       <c r="C116" t="n">
         <v>17.36000061035156</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>14.19167041778564</v>
+        <v>14.19166946411133</v>
       </c>
       <c r="C117" t="n">
         <v>16.09000015258789</v>
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.9568452835083</v>
+        <v>12.95684623718262</v>
       </c>
       <c r="C118" t="n">
         <v>14.6899995803833</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>14.79144191741943</v>
+        <v>14.7914457321167</v>
       </c>
       <c r="C119" t="n">
         <v>16.77000045776367</v>
@@ -3390,7 +3402,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>16.56063079833984</v>
+        <v>16.56063270568848</v>
       </c>
       <c r="C121" t="n">
         <v>18.67000007629395</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>15.65586948394775</v>
+        <v>15.6558723449707</v>
       </c>
       <c r="C122" t="n">
         <v>17.64999961853027</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>16.82855987548828</v>
+        <v>16.82856369018555</v>
       </c>
       <c r="C123" t="n">
         <v>18.8700008392334</v>
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>18.88865852355957</v>
+        <v>18.88865661621094</v>
       </c>
       <c r="C124" t="n">
         <v>21.18000030517578</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>18.25547027587891</v>
+        <v>18.25546455383301</v>
       </c>
       <c r="C125" t="n">
         <v>20.46999931335449</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>21.87364768981934</v>
+        <v>21.87365531921387</v>
       </c>
       <c r="C126" t="n">
         <v>24.42000007629395</v>
@@ -3593,11 +3605,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>21.4705753326416</v>
+        <v>21.47057342529297</v>
       </c>
       <c r="C127" t="n">
         <v>23.96999931335449</v>
@@ -3622,7 +3634,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>26.82050704956055</v>
+        <v>26.82050895690918</v>
       </c>
       <c r="C129" t="n">
         <v>29.84000015258789</v>
@@ -3680,11 +3692,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>27.0991325378418</v>
+        <v>27.09913635253906</v>
       </c>
       <c r="C130" t="n">
         <v>30.14999961853027</v>
@@ -3709,7 +3721,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>29.03431129455566</v>
+        <v>29.0343074798584</v>
       </c>
       <c r="C132" t="n">
         <v>32.20000076293945</v>
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>29.0974235534668</v>
+        <v>29.09742736816406</v>
       </c>
       <c r="C133" t="n">
         <v>32.27000045776367</v>
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.88276672363281</v>
+        <v>30.88276290893555</v>
       </c>
       <c r="C134" t="n">
         <v>34.25</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>32.75219345092773</v>
+        <v>32.75218200683594</v>
       </c>
       <c r="C135" t="n">
         <v>36.22000122070312</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>35.17560577392578</v>
+        <v>35.17557907104492</v>
       </c>
       <c r="C136" t="n">
         <v>38.90000152587891</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.72187042236328</v>
+        <v>36.72187805175781</v>
       </c>
       <c r="C137" t="n">
         <v>40.61000061035156</v>
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>41.58027648925781</v>
+        <v>41.58025741577148</v>
       </c>
       <c r="C138" t="n">
         <v>45.88000106811523</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>37.43856811523438</v>
+        <v>37.43855285644531</v>
       </c>
       <c r="C139" t="n">
         <v>41.31000137329102</v>
@@ -3970,7 +3982,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3999,7 +4011,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>47.31754684448242</v>
+        <v>47.31753921508789</v>
       </c>
       <c r="C142" t="n">
         <v>52.09000015258789</v>
@@ -4057,11 +4069,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.25991821289062</v>
+        <v>51.25992202758789</v>
       </c>
       <c r="C143" t="n">
         <v>56.43000030517578</v>
@@ -4086,7 +4098,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>46.51552200317383</v>
+        <v>46.51553726196289</v>
       </c>
       <c r="C145" t="n">
         <v>51.11999893188477</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>48.79944610595703</v>
+        <v>48.7994499206543</v>
       </c>
       <c r="C146" t="n">
         <v>53.63000106811523</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>52.49815368652344</v>
+        <v>52.4981575012207</v>
       </c>
       <c r="C147" t="n">
         <v>57.59000015258789</v>
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>50.69321823120117</v>
+        <v>50.69322204589844</v>
       </c>
       <c r="C148" t="n">
         <v>55.61000061035156</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>45.27839660644531</v>
+        <v>45.27840805053711</v>
       </c>
       <c r="C149" t="n">
         <v>49.66999816894531</v>
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>46.47524261474609</v>
+        <v>46.47523880004883</v>
       </c>
       <c r="C150" t="n">
         <v>50.77999877929688</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.27434158325195</v>
+        <v>42.27435684204102</v>
       </c>
       <c r="C151" t="n">
         <v>46.18999862670898</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>44.50750350952148</v>
+        <v>44.50749969482422</v>
       </c>
       <c r="C152" t="n">
         <v>48.63000106811523</v>
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.55384826660156</v>
+        <v>39.55385589599609</v>
       </c>
       <c r="C153" t="n">
         <v>43.02000045776367</v>
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>35.53593444824219</v>
+        <v>35.53594970703125</v>
       </c>
       <c r="C154" t="n">
         <v>38.65000152587891</v>
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.2308406829834</v>
+        <v>30.23084259033203</v>
       </c>
       <c r="C155" t="n">
         <v>32.88000106811523</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>34.46906661987305</v>
+        <v>34.46905136108398</v>
       </c>
       <c r="C156" t="n">
         <v>37.27999877929688</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>30.27138328552246</v>
+        <v>30.2713737487793</v>
       </c>
       <c r="C157" t="n">
         <v>32.7400016784668</v>
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>36.13333511352539</v>
+        <v>36.13333129882812</v>
       </c>
       <c r="C158" t="n">
         <v>39.08000183105469</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.63046264648438</v>
+        <v>35.63045501708984</v>
       </c>
       <c r="C159" t="n">
         <v>38.34000015258789</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>36.857177734375</v>
+        <v>36.85717391967773</v>
       </c>
       <c r="C160" t="n">
         <v>39.65999984741211</v>
@@ -4579,7 +4591,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>36.13962173461914</v>
+        <v>36.13961791992188</v>
       </c>
       <c r="C162" t="n">
         <v>38.68999862670898</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.94960403442383</v>
+        <v>41.94960784912109</v>
       </c>
       <c r="C163" t="n">
         <v>44.90999984741211</v>
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.1156005859375</v>
+        <v>46.11560821533203</v>
       </c>
       <c r="C164" t="n">
         <v>49.36999893188477</v>
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>45.05708694458008</v>
+        <v>45.05707168579102</v>
       </c>
       <c r="C165" t="n">
         <v>48.02000045776367</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>46.82106781005859</v>
+        <v>46.82108306884766</v>
       </c>
       <c r="C166" t="n">
         <v>49.90000152587891</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>50.91205215454102</v>
+        <v>50.91205978393555</v>
       </c>
       <c r="C167" t="n">
         <v>54.2599983215332</v>
@@ -4782,7 +4794,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4811,7 +4823,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.60006713867188</v>
+        <v>54.60006332397461</v>
       </c>
       <c r="C170" t="n">
         <v>57.9900016784668</v>
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4898,7 +4910,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.92323303222656</v>
+        <v>46.92324447631836</v>
       </c>
       <c r="C173" t="n">
         <v>49.68000030517578</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>53.27384567260742</v>
+        <v>53.27383804321289</v>
       </c>
       <c r="C174" t="n">
         <v>56.18000030517578</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>57.32296371459961</v>
+        <v>57.32295989990234</v>
       </c>
       <c r="C175" t="n">
         <v>60.45000076293945</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>61.00225830078125</v>
+        <v>61.00225448608398</v>
       </c>
       <c r="C176" t="n">
         <v>64.33000183105469</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>58.60756301879883</v>
+        <v>58.60757446289062</v>
       </c>
       <c r="C177" t="n">
         <v>61.59999847412109</v>
@@ -5072,7 +5084,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5101,7 +5113,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>78.70606994628906</v>
+        <v>78.7060546875</v>
       </c>
       <c r="C180" t="n">
         <v>82.48000335693359</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>82.35128784179688</v>
+        <v>82.35129547119141</v>
       </c>
       <c r="C181" t="n">
         <v>86.30000305175781</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>92.25634765625</v>
+        <v>92.25633239746094</v>
       </c>
       <c r="C182" t="n">
         <v>96.68000030517578</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>112.9961929321289</v>
+        <v>112.996208190918</v>
       </c>
       <c r="C183" t="n">
         <v>118.1900024414062</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>127.7289962768555</v>
+        <v>127.7290191650391</v>
       </c>
       <c r="C184" t="n">
         <v>133.6000061035156</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>126.8781509399414</v>
+        <v>126.8781127929688</v>
       </c>
       <c r="C185" t="n">
         <v>132.7100067138672</v>
@@ -5304,7 +5316,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>136.3803100585938</v>
+        <v>136.3803405761719</v>
       </c>
       <c r="C187" t="n">
         <v>142.3999938964844</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>134.0147552490234</v>
+        <v>134.0147247314453</v>
       </c>
       <c r="C188" t="n">
         <v>139.9299926757812</v>
@@ -5391,7 +5403,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>123.5137176513672</v>
+        <v>123.5137252807617</v>
       </c>
       <c r="C190" t="n">
         <v>128.7299957275391</v>
@@ -5449,7 +5461,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5478,7 +5490,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>151.2273254394531</v>
+        <v>151.2273559570312</v>
       </c>
       <c r="C193" t="n">
         <v>157.3600006103516</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>132.7948303222656</v>
+        <v>132.7947998046875</v>
       </c>
       <c r="C194" t="n">
         <v>138.1799926757812</v>
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>129.2024230957031</v>
+        <v>129.2024688720703</v>
       </c>
       <c r="C195" t="n">
         <v>134.1999969482422</v>
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>106.2406234741211</v>
+        <v>106.2406311035156</v>
       </c>
       <c r="C197" t="n">
         <v>110.3499984741211</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>113.1982955932617</v>
+        <v>113.1983032226562</v>
       </c>
       <c r="C198" t="n">
         <v>117.2900009155273</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>87.80613708496094</v>
+        <v>87.80615234375</v>
       </c>
       <c r="C199" t="n">
         <v>90.98000335693359</v>
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>102.2828598022461</v>
+        <v>102.2828674316406</v>
       </c>
       <c r="C200" t="n">
         <v>105.9800033569336</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>91.02051544189453</v>
+        <v>91.02052307128906</v>
       </c>
       <c r="C201" t="n">
         <v>94.06999969482422</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>79.27405548095703</v>
+        <v>79.27407073974609</v>
       </c>
       <c r="C202" t="n">
         <v>81.93000030517578</v>
@@ -5797,7 +5809,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>106.305290222168</v>
+        <v>106.3052978515625</v>
       </c>
       <c r="C204" t="n">
         <v>109.5999984741211</v>
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>94.45265197753906</v>
+        <v>94.45264434814453</v>
       </c>
       <c r="C205" t="n">
         <v>97.37999725341797</v>
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>108.1384735107422</v>
+        <v>108.1384811401367</v>
       </c>
       <c r="C206" t="n">
         <v>111.4899978637695</v>
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>112.9222259521484</v>
+        <v>112.9222412109375</v>
       </c>
       <c r="C207" t="n">
         <v>116.1500015258789</v>
@@ -5942,11 +5954,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>119.4165802001953</v>
+        <v>119.4165954589844</v>
       </c>
       <c r="C208" t="n">
         <v>122.8300018310547</v>
@@ -5971,7 +5983,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6000,7 +6012,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>140.8854370117188</v>
+        <v>140.8854064941406</v>
       </c>
       <c r="C211" t="n">
         <v>144.5399932861328</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>147.7571868896484</v>
+        <v>147.7571716308594</v>
       </c>
       <c r="C212" t="n">
         <v>151.5899963378906</v>
@@ -6087,7 +6099,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>135.2421417236328</v>
+        <v>135.2421264648438</v>
       </c>
       <c r="C214" t="n">
         <v>138.4499969482422</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>129.2834930419922</v>
+        <v>129.2834625244141</v>
       </c>
       <c r="C215" t="n">
         <v>132.3500061035156</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>146.6239776611328</v>
+        <v>146.6239471435547</v>
       </c>
       <c r="C216" t="n">
         <v>149.7799987792969</v>
@@ -6203,11 +6215,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>158.6550445556641</v>
+        <v>158.6550140380859</v>
       </c>
       <c r="C217" t="n">
         <v>162.0700073242188</v>
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>197.7061462402344</v>
+        <v>197.7061309814453</v>
       </c>
       <c r="C219" t="n">
         <v>201.6199951171875</v>
@@ -6290,7 +6302,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>194.7937927246094</v>
+        <v>194.7937774658203</v>
       </c>
       <c r="C221" t="n">
         <v>198.6499938964844</v>
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>211.2893981933594</v>
+        <v>211.2893676757812</v>
       </c>
       <c r="C222" t="n">
         <v>215.0800018310547</v>
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>231.8308410644531</v>
+        <v>231.8308563232422</v>
       </c>
       <c r="C223" t="n">
         <v>235.9900054931641</v>
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>208.4601287841797</v>
+        <v>208.4601135253906</v>
       </c>
       <c r="C224" t="n">
         <v>212.1999969482422</v>
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>194.15478515625</v>
+        <v>194.1548309326172</v>
       </c>
       <c r="C225" t="n">
         <v>197.2599945068359</v>
@@ -6464,11 +6476,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>198.8694000244141</v>
+        <v>198.8694152832031</v>
       </c>
       <c r="C226" t="n">
         <v>202.0500030517578</v>
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>178.7216339111328</v>
+        <v>178.7216186523438</v>
       </c>
       <c r="C227" t="n">
         <v>181.5800018310547</v>
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>172.3641815185547</v>
+        <v>172.3641967773438</v>
       </c>
       <c r="C228" t="n">
         <v>174.7100067138672</v>
@@ -6551,7 +6563,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6580,7 +6592,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>143.5012359619141</v>
+        <v>143.5012512207031</v>
       </c>
       <c r="C232" t="n">
         <v>145.1199951171875</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>149.0289154052734</v>
+        <v>149.0289001464844</v>
       </c>
       <c r="C233" t="n">
         <v>150.7100067138672</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>155.4422607421875</v>
+        <v>155.4422912597656</v>
       </c>
       <c r="C234" t="n">
         <v>156.75</v>
@@ -6725,7 +6737,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6754,7 +6766,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6841,11 +6853,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>231.8178100585938</v>
+        <v>231.8177947998047</v>
       </c>
       <c r="C239" t="n">
         <v>233.1000061035156</v>
@@ -6870,11 +6882,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>251.3542022705078</v>
+        <v>251.3542175292969</v>
       </c>
       <c r="C240" t="n">
         <v>252.25</v>
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>474.3800048828125</v>
+        <v>474.25</v>
       </c>
       <c r="C250" t="n">
-        <v>474.3800048828125</v>
+        <v>474.25</v>
       </c>
       <c r="D250" t="n">
-        <v>105376000</v>
+        <v>109535900</v>
       </c>
       <c r="E250" t="n">
         <v>11.58</v>
       </c>
       <c r="F250" t="n">
-        <v>40.96545810732405</v>
+        <v>40.95423143350605</v>
       </c>
       <c r="G250" t="n">
         <v>793597443</v>
       </c>
       <c r="H250" t="n">
-        <v>376466758885.3275</v>
+        <v>376363587342.75</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1327826858938103</v>
+        <v>0.1380245122589187</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39566</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39656</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39748</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39838</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40246</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39839</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39929</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40338</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39930</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40020</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40021</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40111</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7480,7 +7492,7 @@
       <c r="I6" t="n">
         <v>-0.23</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="K6" t="n">
@@ -7493,13 +7505,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40112</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40246</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7526,7 +7538,7 @@
       <c r="I7" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="K7" t="n">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40338</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7572,7 +7584,7 @@
       <c r="I8" t="n">
         <v>0.32</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="K8" t="n">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40424</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7618,7 +7630,7 @@
       <c r="I9" t="n">
         <v>0.45</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="K9" t="n">
@@ -7631,13 +7643,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7664,7 +7676,7 @@
       <c r="I10" t="n">
         <v>0.7</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="K10" t="n">
@@ -7677,13 +7689,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7710,7 +7722,7 @@
       <c r="I11" t="n">
         <v>1.02</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7723,13 +7735,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7756,7 +7768,7 @@
       <c r="I12" t="n">
         <v>1.186841710427607</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="K12" t="n">
@@ -7769,13 +7781,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7802,7 +7814,7 @@
       <c r="I13" t="n">
         <v>1.456841710427607</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="K13" t="n">
@@ -7815,13 +7827,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40883</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7848,7 +7860,7 @@
       <c r="I14" t="n">
         <v>1.446841710427607</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40883</v>
       </c>
       <c r="K14" t="n">
@@ -7861,13 +7873,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7894,7 +7906,7 @@
       <c r="I15" t="n">
         <v>1.156154687526844</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K15" t="n">
@@ -7907,13 +7919,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40938</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7940,7 +7952,7 @@
       <c r="I16" t="n">
         <v>1.011449794931673</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="K16" t="n">
@@ -7953,13 +7965,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7986,7 +7998,7 @@
       <c r="I17" t="n">
         <v>0.8214497949316732</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="K17" t="n">
@@ -7999,13 +8011,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41120</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8032,7 +8044,7 @@
       <c r="I18" t="n">
         <v>0.06144979493167324</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="K18" t="n">
@@ -8045,13 +8057,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41301</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8078,7 +8090,7 @@
       <c r="I19" t="n">
         <v>0.0001896231129646583</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K19" t="n">
@@ -8091,13 +8103,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41302</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41392</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41417</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8124,7 +8136,7 @@
       <c r="I20" t="n">
         <v>-0.3291791149189732</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41417</v>
       </c>
       <c r="K20" t="n">
@@ -8137,13 +8149,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41393</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41483</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41508</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8170,7 +8182,7 @@
       <c r="I21" t="n">
         <v>-0.3591791149189731</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41508</v>
       </c>
       <c r="K21" t="n">
@@ -8183,13 +8195,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41484</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41574</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41612</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8216,7 +8228,7 @@
       <c r="I22" t="n">
         <v>0.2108208850810268</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41612</v>
       </c>
       <c r="K22" t="n">
@@ -8229,13 +8241,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41575</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41665</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8262,7 +8274,7 @@
       <c r="I23" t="n">
         <v>0.3892986920453967</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K23" t="n">
@@ -8275,13 +8287,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41666</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41756</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8308,7 +8320,7 @@
       <c r="I24" t="n">
         <v>0.7065306122448979</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="K24" t="n">
@@ -8321,13 +8333,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41847</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41872</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8354,7 +8366,7 @@
       <c r="I25" t="n">
         <v>0.8065306122448979</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41872</v>
       </c>
       <c r="K25" t="n">
@@ -8367,13 +8379,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41938</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8400,7 +8412,7 @@
       <c r="I26" t="n">
         <v>0.8665306122448979</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="K26" t="n">
@@ -8413,13 +8425,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42029</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8446,7 +8458,7 @@
       <c r="I27" t="n">
         <v>0.9406451612903226</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K27" t="n">
@@ -8459,13 +8471,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42030</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42120</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42145</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8492,7 +8504,7 @@
       <c r="I28" t="n">
         <v>1.020645161290322</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42145</v>
       </c>
       <c r="K28" t="n">
@@ -8505,13 +8517,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42121</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42211</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42236</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="I29" t="n">
         <v>1.050645161290323</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42236</v>
       </c>
       <c r="K29" t="n">
@@ -8551,13 +8563,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42302</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8584,7 +8596,7 @@
       <c r="I30" t="n">
         <v>1.120645161290323</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="K30" t="n">
@@ -8597,13 +8609,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8630,7 +8642,7 @@
       <c r="I31" t="n">
         <v>1.087833622183709</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8643,13 +8655,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8676,7 +8688,7 @@
       <c r="I32" t="n">
         <v>1.087833622183709</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="K32" t="n">
@@ -8689,13 +8701,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42492</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42607</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8722,7 +8734,7 @@
       <c r="I33" t="n">
         <v>1.277833622183709</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42607</v>
       </c>
       <c r="K33" t="n">
@@ -8735,13 +8747,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8768,7 +8780,7 @@
       <c r="I34" t="n">
         <v>1.557833622183709</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="K34" t="n">
@@ -8781,13 +8793,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8814,7 +8826,7 @@
       <c r="I35" t="n">
         <v>1.9555463728191</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8827,13 +8839,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42880</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8860,7 +8872,7 @@
       <c r="I36" t="n">
         <v>2.4255463728191</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42880</v>
       </c>
       <c r="K36" t="n">
@@ -8873,13 +8885,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42971</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8906,7 +8918,7 @@
       <c r="I37" t="n">
         <v>2.8155463728191</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42971</v>
       </c>
       <c r="K37" t="n">
@@ -8919,13 +8931,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8952,7 +8964,7 @@
       <c r="I38" t="n">
         <v>3.1655463728191</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="K38" t="n">
@@ -8965,13 +8977,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="I39" t="n">
         <v>2.646050420168067</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K39" t="n">
@@ -9011,13 +9023,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9044,7 +9056,7 @@
       <c r="I40" t="n">
         <v>2.976050420168067</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="K40" t="n">
@@ -9057,13 +9069,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43335</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9090,7 +9102,7 @@
       <c r="I41" t="n">
         <v>3.296050420168068</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43335</v>
       </c>
       <c r="K41" t="n">
@@ -9103,13 +9115,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43401</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9136,7 +9148,7 @@
       <c r="I42" t="n">
         <v>3.276050420168068</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="K42" t="n">
@@ -9149,13 +9161,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9182,7 +9194,7 @@
       <c r="I43" t="n">
         <v>3.95</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9195,13 +9207,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9228,7 +9240,7 @@
       <c r="I44" t="n">
         <v>3.56</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="K44" t="n">
@@ -9241,13 +9253,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43699</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9274,7 +9286,7 @@
       <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43699</v>
       </c>
       <c r="K45" t="n">
@@ -9287,13 +9299,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43765</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9320,7 +9332,7 @@
       <c r="I46" t="n">
         <v>2.86</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="K46" t="n">
@@ -9333,13 +9345,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43766</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43856</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9366,7 +9378,7 @@
       <c r="I47" t="n">
         <v>3.02</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K47" t="n">
@@ -9379,13 +9391,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43857</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43947</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9412,7 +9424,7 @@
       <c r="I48" t="n">
         <v>3.14</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="K48" t="n">
@@ -9425,13 +9437,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44038</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44063</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9458,7 +9470,7 @@
       <c r="I49" t="n">
         <v>3.44</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44063</v>
       </c>
       <c r="K49" t="n">
@@ -9471,13 +9483,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44129</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="I50" t="n">
         <v>3.92</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="K50" t="n">
@@ -9517,13 +9529,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9550,7 +9562,7 @@
       <c r="I51" t="n">
         <v>4.18</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9563,13 +9575,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9596,7 +9608,7 @@
       <c r="I52" t="n">
         <v>4.79</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="K52" t="n">
@@ -9609,13 +9621,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9642,7 +9654,7 @@
       <c r="I53" t="n">
         <v>5.75</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="K53" t="n">
@@ -9655,13 +9667,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9688,7 +9700,7 @@
       <c r="I54" t="n">
         <v>6.4</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="K54" t="n">
@@ -9701,13 +9713,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9734,7 +9746,7 @@
       <c r="I55" t="n">
         <v>7.180000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9747,13 +9759,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9780,7 +9792,7 @@
       <c r="I56" t="n">
         <v>7.490000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="K56" t="n">
@@ -9793,13 +9805,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="I57" t="n">
         <v>7.470000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="K57" t="n">
@@ -9839,13 +9851,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9872,7 +9884,7 @@
       <c r="I58" t="n">
         <v>7.44</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="K58" t="n">
@@ -9885,13 +9897,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9918,7 +9930,7 @@
       <c r="I59" t="n">
         <v>7.460000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9931,13 +9943,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44956</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9964,7 +9976,7 @@
       <c r="I60" t="n">
         <v>7.580000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="K60" t="n">
@@ -9977,13 +9989,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10010,7 +10022,7 @@
       <c r="I61" t="n">
         <v>7.580000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="K61" t="n">
@@ -10023,13 +10035,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10056,7 +10068,7 @@
       <c r="I62" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="K62" t="n">
@@ -10069,13 +10081,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10102,7 +10114,7 @@
       <c r="I63" t="n">
         <v>8.5</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="K63" t="n">
@@ -10115,13 +10127,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="I64" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="K64" t="n">
@@ -10161,13 +10173,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10194,7 +10206,7 @@
       <c r="I65" t="n">
         <v>8.899999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="K65" t="n">
@@ -10207,13 +10219,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45592</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10240,7 +10252,7 @@
       <c r="I66" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="K66" t="n">
@@ -10253,13 +10265,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="I67" t="n">
         <v>7.649999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K67" t="n">
@@ -10299,13 +10311,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10332,7 +10344,7 @@
       <c r="I68" t="n">
         <v>8.219999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="K68" t="n">
@@ -10345,13 +10357,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10378,7 +10390,7 @@
       <c r="I69" t="n">
         <v>8.389999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="K69" t="n">
@@ -10391,13 +10403,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10424,7 +10436,7 @@
       <c r="I70" t="n">
         <v>8.659999999999998</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="K70" t="n">
@@ -10437,13 +10449,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46047</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10470,7 +10482,7 @@
       <c r="I71" t="n">
         <v>9.75</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10483,13 +10495,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10516,7 +10528,7 @@
       <c r="I72" t="n">
         <v>10.63</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="K72" t="n">
@@ -10529,13 +10541,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46229</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10562,7 +10574,7 @@
       <c r="I73" t="n">
         <v>11.58</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="K73" t="n">
@@ -10599,52 +10611,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40020</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="C2" t="n">
@@ -10673,10 +10685,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40137</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40158</v>
       </c>
       <c r="C3" t="n">
@@ -10705,10 +10717,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40246</v>
       </c>
       <c r="C4" t="n">
@@ -10737,10 +10749,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40338</v>
       </c>
       <c r="C5" t="n">
@@ -10769,10 +10781,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40424</v>
       </c>
       <c r="C6" t="n">
@@ -10801,10 +10813,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40501</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="C7" t="n">
@@ -10833,10 +10845,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10865,10 +10877,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="C9" t="n">
@@ -10897,10 +10909,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40781</v>
       </c>
       <c r="C10" t="n">
@@ -10929,10 +10941,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40867</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40883</v>
       </c>
       <c r="C11" t="n">
@@ -10961,10 +10973,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C12" t="n">
@@ -10993,10 +11005,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="C13" t="n">
@@ -11025,10 +11037,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="C14" t="n">
@@ -11057,10 +11069,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41234</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="C15" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41301</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -11121,10 +11133,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41392</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41417</v>
       </c>
       <c r="C17" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41483</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41508</v>
       </c>
       <c r="C18" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41599</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41612</v>
       </c>
       <c r="C19" t="n">
@@ -11217,10 +11229,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C20" t="n">
@@ -11249,10 +11261,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41768</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="C21" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41847</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41872</v>
       </c>
       <c r="C22" t="n">
@@ -11313,10 +11325,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41985</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="C23" t="n">
@@ -11345,10 +11357,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42046</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C24" t="n">
@@ -11377,10 +11389,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42120</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42145</v>
       </c>
       <c r="C25" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42211</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42236</v>
       </c>
       <c r="C26" t="n">
@@ -11441,10 +11453,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42341</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="C27" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11505,10 +11517,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="C29" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42607</v>
       </c>
       <c r="C30" t="n">
@@ -11569,10 +11581,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42712</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="C31" t="n">
@@ -11601,10 +11613,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11633,10 +11645,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42880</v>
       </c>
       <c r="C33" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42971</v>
       </c>
       <c r="C34" t="n">
@@ -11697,10 +11709,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43077</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="C35" t="n">
@@ -11729,10 +11741,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="C37" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43335</v>
       </c>
       <c r="C38" t="n">
@@ -11825,10 +11837,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43441</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="C39" t="n">
@@ -11857,10 +11869,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11889,10 +11901,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="C41" t="n">
@@ -11921,10 +11933,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43699</v>
       </c>
       <c r="C42" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43805</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="C43" t="n">
@@ -11985,10 +11997,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43856</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -12017,10 +12029,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43947</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="C45" t="n">
@@ -12049,10 +12061,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44038</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44063</v>
       </c>
       <c r="C46" t="n">
@@ -12081,10 +12093,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44169</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="C47" t="n">
@@ -12113,10 +12125,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12145,10 +12157,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="C49" t="n">
@@ -12177,10 +12189,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="C50" t="n">
@@ -12209,10 +12221,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44540</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="C51" t="n">
@@ -12241,10 +12253,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12273,10 +12285,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="C53" t="n">
@@ -12305,10 +12317,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="C54" t="n">
@@ -12337,10 +12349,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44904</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="C55" t="n">
@@ -12369,10 +12381,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12401,10 +12413,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C57" t="n">
@@ -12433,10 +12445,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="C58" t="n">
@@ -12465,10 +12477,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45268</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="C59" t="n">
@@ -12497,10 +12509,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="C60" t="n">
@@ -12529,10 +12541,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="C61" t="n">
@@ -12561,10 +12573,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45526</v>
       </c>
       <c r="C62" t="n">
@@ -12593,10 +12605,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45632</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="C63" t="n">
@@ -12625,10 +12637,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C64" t="n">
@@ -12657,10 +12669,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="C65" t="n">
@@ -12689,10 +12701,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="C66" t="n">
@@ -12721,10 +12733,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="C67" t="n">
@@ -12753,10 +12765,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46047</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12785,10 +12797,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="C69" t="n">
@@ -12817,10 +12829,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46229</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="C70" t="n">
@@ -12867,12 +12879,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AMAT.xlsx
+++ b/salidas/empresas/AMAT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.82302474975586</v>
+        <v>13.82301807403564</v>
       </c>
       <c r="C2" t="n">
         <v>19.04999923706055</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31342887878418</v>
+        <v>13.31342792510986</v>
       </c>
       <c r="C3" t="n">
         <v>18.31999969482422</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.04454803466797</v>
+        <v>13.04454612731934</v>
       </c>
       <c r="C5" t="n">
         <v>17.95000076293945</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.32347679138184</v>
+        <v>12.32347869873047</v>
       </c>
       <c r="C6" t="n">
         <v>16.90999984741211</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.4853982925415</v>
+        <v>11.48539447784424</v>
       </c>
       <c r="C8" t="n">
         <v>15.76000022888184</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.35631275177002</v>
+        <v>12.35630702972412</v>
       </c>
       <c r="C9" t="n">
         <v>16.89999961853027</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.96316051483154</v>
+        <v>12.96315574645996</v>
       </c>
       <c r="C10" t="n">
         <v>17.72999954223633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.71457290649414</v>
+        <v>12.71456432342529</v>
       </c>
       <c r="C11" t="n">
         <v>17.38999938964844</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>13.20434856414795</v>
+        <v>13.20435333251953</v>
       </c>
       <c r="C12" t="n">
         <v>18.01000022888184</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52694797515869</v>
+        <v>13.52694416046143</v>
       </c>
       <c r="C13" t="n">
         <v>18.45000076293945</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.99906444549561</v>
+        <v>12.99906635284424</v>
       </c>
       <c r="C14" t="n">
         <v>17.72999954223633</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.65308475494385</v>
+        <v>13.6530818939209</v>
       </c>
       <c r="C15" t="n">
         <v>18.56999969482422</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.46927452087402</v>
+        <v>13.46927356719971</v>
       </c>
       <c r="C16" t="n">
         <v>18.31999969482422</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.08401298522949</v>
+        <v>14.08401870727539</v>
       </c>
       <c r="C18" t="n">
         <v>19.10000038146973</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.65179920196533</v>
+        <v>14.65180206298828</v>
       </c>
       <c r="C19" t="n">
         <v>19.8700008392334</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.25192070007324</v>
+        <v>16.25191688537598</v>
       </c>
       <c r="C20" t="n">
         <v>22.04000091552734</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.79409027099609</v>
+        <v>15.79408931732178</v>
       </c>
       <c r="C21" t="n">
         <v>21.36000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.30607414245605</v>
+        <v>15.30606460571289</v>
       </c>
       <c r="C22" t="n">
         <v>20.70000076293945</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.35960578918457</v>
+        <v>14.35960388183594</v>
       </c>
       <c r="C23" t="n">
         <v>19.42000007629395</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>13.96912574768066</v>
+        <v>13.9691219329834</v>
       </c>
       <c r="C24" t="n">
         <v>18.82999992370605</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>13.17533302307129</v>
+        <v>13.17533779144287</v>
       </c>
       <c r="C25" t="n">
         <v>17.76000022888184</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>13.29403209686279</v>
+        <v>13.29403972625732</v>
       </c>
       <c r="C26" t="n">
         <v>17.92000007629395</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.26764869689941</v>
+        <v>14.2676477432251</v>
       </c>
       <c r="C27" t="n">
         <v>19.17000007629395</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>14.52070140838623</v>
+        <v>14.52070045471191</v>
       </c>
       <c r="C28" t="n">
         <v>19.51000022888184</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.88807201385498</v>
+        <v>13.88807964324951</v>
       </c>
       <c r="C29" t="n">
         <v>18.65999984741211</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.78864574432373</v>
+        <v>14.78864479064941</v>
       </c>
       <c r="C30" t="n">
         <v>19.80999946594238</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.25114631652832</v>
+        <v>14.25114154815674</v>
       </c>
       <c r="C31" t="n">
         <v>19.09000015258789</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>12.92979907989502</v>
+        <v>12.92979621887207</v>
       </c>
       <c r="C32" t="n">
         <v>17.31999969482422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.42119121551514</v>
+        <v>13.4211950302124</v>
       </c>
       <c r="C33" t="n">
         <v>17.92000007629395</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>11.33162117004395</v>
+        <v>11.33162403106689</v>
       </c>
       <c r="C34" t="n">
         <v>15.13000011444092</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>9.668949127197266</v>
+        <v>9.668951034545898</v>
       </c>
       <c r="C35" t="n">
         <v>12.90999984741211</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.213242530822754</v>
+        <v>7.213245391845703</v>
       </c>
       <c r="C36" t="n">
         <v>9.579999923706055</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.627368450164795</v>
+        <v>7.627366065979004</v>
       </c>
       <c r="C37" t="n">
         <v>10.13000011444092</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.055124759674072</v>
+        <v>7.05512523651123</v>
       </c>
       <c r="C38" t="n">
         <v>9.369999885559082</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.975687026977539</v>
+        <v>6.975688934326172</v>
       </c>
       <c r="C39" t="n">
         <v>9.210000038146973</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.142095565795898</v>
+        <v>8.142087936401367</v>
       </c>
       <c r="C40" t="n">
         <v>10.75</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.247896194458008</v>
+        <v>9.247900009155273</v>
       </c>
       <c r="C41" t="n">
         <v>12.21000003814697</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.572028160095215</v>
+        <v>8.572026252746582</v>
       </c>
       <c r="C42" t="n">
         <v>11.26000022888184</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.381702423095703</v>
+        <v>8.381706237792969</v>
       </c>
       <c r="C43" t="n">
         <v>11.01000022888184</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>10.50568389892578</v>
+        <v>10.50568008422852</v>
       </c>
       <c r="C44" t="n">
         <v>13.80000019073486</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.0783805847168</v>
+        <v>10.07837772369385</v>
       </c>
       <c r="C45" t="n">
         <v>13.18000030517578</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.23131275177002</v>
+        <v>10.23131656646729</v>
       </c>
       <c r="C46" t="n">
         <v>13.38000011444092</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.32900333404541</v>
+        <v>9.329000473022461</v>
       </c>
       <c r="C47" t="n">
         <v>12.19999980926514</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>10.7113618850708</v>
+        <v>10.71135997772217</v>
       </c>
       <c r="C49" t="n">
         <v>13.9399995803833</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.358994483947754</v>
+        <v>9.35899543762207</v>
       </c>
       <c r="C50" t="n">
         <v>12.18000030517578</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>9.450457572937012</v>
+        <v>9.450460433959961</v>
       </c>
       <c r="C51" t="n">
         <v>12.23999977111816</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>10.63949012756348</v>
+        <v>10.63948822021484</v>
       </c>
       <c r="C53" t="n">
         <v>13.77999973297119</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>10.03068542480469</v>
+        <v>10.03068065643311</v>
       </c>
       <c r="C54" t="n">
         <v>12.92000007629395</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>9.331957817077637</v>
+        <v>9.331951141357422</v>
       </c>
       <c r="C55" t="n">
         <v>12.02000045776367</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>9.161149978637695</v>
+        <v>9.161154747009277</v>
       </c>
       <c r="C56" t="n">
         <v>11.80000019073486</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.102083206176758</v>
+        <v>8.102086067199707</v>
       </c>
       <c r="C57" t="n">
         <v>10.36999988555908</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.125585556030273</v>
+        <v>9.125591278076172</v>
       </c>
       <c r="C58" t="n">
         <v>11.68000030517578</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.76612377166748</v>
+        <v>9.766124725341797</v>
       </c>
       <c r="C60" t="n">
         <v>12.43000030517578</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>11.03893661499023</v>
+        <v>11.0389404296875</v>
       </c>
       <c r="C61" t="n">
         <v>14.05000019073486</v>
@@ -1738,7 +1738,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>12.32746887207031</v>
+        <v>12.32747459411621</v>
       </c>
       <c r="C62" t="n">
         <v>15.6899995803833</v>
@@ -1767,7 +1767,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.96518325805664</v>
+        <v>12.96518135070801</v>
       </c>
       <c r="C63" t="n">
         <v>16.43000030517578</v>
@@ -1796,7 +1796,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>12.32599830627441</v>
+        <v>12.32599925994873</v>
       </c>
       <c r="C64" t="n">
         <v>15.61999988555908</v>
@@ -1825,7 +1825,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>12.38123416900635</v>
+        <v>12.3812370300293</v>
       </c>
       <c r="C65" t="n">
         <v>15.6899995803833</v>
@@ -1854,7 +1854,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.93817806243896</v>
+        <v>10.93817710876465</v>
       </c>
       <c r="C66" t="n">
         <v>13.77999973297119</v>
@@ -1883,7 +1883,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.32697582244873</v>
+        <v>10.32697200775146</v>
       </c>
       <c r="C67" t="n">
         <v>13.01000022888184</v>
@@ -1912,7 +1912,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>9.77927303314209</v>
+        <v>9.779266357421875</v>
       </c>
       <c r="C68" t="n">
         <v>12.31999969482422</v>
@@ -1970,7 +1970,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.283390045166016</v>
+        <v>8.283393859863281</v>
       </c>
       <c r="C70" t="n">
         <v>10.35999965667725</v>
@@ -1999,7 +1999,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.850522041320801</v>
+        <v>9.850523948669434</v>
       </c>
       <c r="C71" t="n">
         <v>12.31999969482422</v>
@@ -2028,7 +2028,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>8.681049346923828</v>
+        <v>8.681051254272461</v>
       </c>
       <c r="C72" t="n">
         <v>10.77999973297119</v>
@@ -2057,7 +2057,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.624679565429688</v>
+        <v>8.624678611755371</v>
       </c>
       <c r="C73" t="n">
         <v>10.71000003814697</v>
@@ -2086,7 +2086,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>9.888984680175781</v>
+        <v>9.888983726501465</v>
       </c>
       <c r="C74" t="n">
         <v>12.27999973297119</v>
@@ -2115,7 +2115,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.92595386505127</v>
+        <v>9.925958633422852</v>
       </c>
       <c r="C75" t="n">
         <v>12.25</v>
@@ -2144,7 +2144,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.08800983428955</v>
+        <v>10.08800792694092</v>
       </c>
       <c r="C76" t="n">
         <v>12.44999980926514</v>
@@ -2202,7 +2202,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>8.441483497619629</v>
+        <v>8.441489219665527</v>
       </c>
       <c r="C78" t="n">
         <v>10.32999992370605</v>
@@ -2231,7 +2231,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.356727600097656</v>
+        <v>9.356728553771973</v>
       </c>
       <c r="C79" t="n">
         <v>11.44999980926514</v>
@@ -2260,7 +2260,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>8.899106979370117</v>
+        <v>8.899110794067383</v>
       </c>
       <c r="C80" t="n">
         <v>10.89000034332275</v>
@@ -2289,7 +2289,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>9.625221252441406</v>
+        <v>9.625224113464355</v>
       </c>
       <c r="C81" t="n">
         <v>11.6899995803833</v>
@@ -2347,7 +2347,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>8.727743148803711</v>
+        <v>8.727746963500977</v>
       </c>
       <c r="C83" t="n">
         <v>10.60000038146973</v>
@@ -2376,7 +2376,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>8.913824081420898</v>
+        <v>8.913819313049316</v>
       </c>
       <c r="C84" t="n">
         <v>10.72999954223633</v>
@@ -2405,7 +2405,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>9.50364875793457</v>
+        <v>9.503645896911621</v>
       </c>
       <c r="C85" t="n">
         <v>11.4399995803833</v>
@@ -2434,7 +2434,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>10.72483539581299</v>
+        <v>10.72483062744141</v>
       </c>
       <c r="C86" t="n">
         <v>12.90999984741211</v>
@@ -2463,7 +2463,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>11.46370697021484</v>
+        <v>11.46370410919189</v>
       </c>
       <c r="C87" t="n">
         <v>13.71000003814697</v>
@@ -2492,7 +2492,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>11.27138423919678</v>
+        <v>11.27138710021973</v>
       </c>
       <c r="C88" t="n">
         <v>13.47999954223633</v>
@@ -2521,7 +2521,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>12.13262557983398</v>
+        <v>12.13262939453125</v>
       </c>
       <c r="C89" t="n">
         <v>14.51000022888184</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>12.55969047546387</v>
+        <v>12.55969142913818</v>
       </c>
       <c r="C91" t="n">
         <v>14.92000007629395</v>
@@ -2604,7 +2604,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>13.73821353912354</v>
+        <v>13.73821544647217</v>
       </c>
       <c r="C92" t="n">
         <v>16.31999969482422</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>12.7172327041626</v>
+        <v>12.71723747253418</v>
       </c>
       <c r="C93" t="n">
         <v>15.01000022888184</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.85230731964111</v>
+        <v>14.85230922698975</v>
       </c>
       <c r="C94" t="n">
         <v>17.53000068664551</v>
@@ -2685,7 +2685,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>15.13189601898193</v>
+        <v>15.13189697265625</v>
       </c>
       <c r="C95" t="n">
         <v>17.86000061035156</v>
@@ -2768,7 +2768,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>14.3353853225708</v>
+        <v>14.3353796005249</v>
       </c>
       <c r="C98" t="n">
         <v>16.81999969482422</v>
@@ -2797,7 +2797,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.24535369873047</v>
+        <v>16.2453556060791</v>
       </c>
       <c r="C99" t="n">
         <v>18.95999908447266</v>
@@ -2826,7 +2826,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.49631881713867</v>
+        <v>17.49631118774414</v>
       </c>
       <c r="C100" t="n">
         <v>20.42000007629395</v>
@@ -2855,7 +2855,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>16.33103561401367</v>
+        <v>16.33103179931641</v>
       </c>
       <c r="C101" t="n">
         <v>19.05999946594238</v>
@@ -2884,7 +2884,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.38566017150879</v>
+        <v>17.38566398620605</v>
       </c>
       <c r="C102" t="n">
         <v>20.19000053405762</v>
@@ -2913,7 +2913,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>19.41785621643066</v>
+        <v>19.41786193847656</v>
       </c>
       <c r="C103" t="n">
         <v>22.54999923706055</v>
@@ -2942,7 +2942,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.0487003326416</v>
+        <v>18.04870414733887</v>
       </c>
       <c r="C104" t="n">
         <v>20.95999908447266</v>
@@ -2971,7 +2971,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.99053382873535</v>
+        <v>19.99053764343262</v>
       </c>
       <c r="C105" t="n">
         <v>23.11000061035156</v>
@@ -3000,7 +3000,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.6930103302002</v>
+        <v>18.6930046081543</v>
       </c>
       <c r="C106" t="n">
         <v>21.61000061035156</v>
@@ -3058,7 +3058,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>20.8966121673584</v>
+        <v>20.89660835266113</v>
       </c>
       <c r="C108" t="n">
         <v>24.04999923706055</v>
@@ -3087,7 +3087,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>21.65253448486328</v>
+        <v>21.65253639221191</v>
       </c>
       <c r="C109" t="n">
         <v>24.92000007629395</v>
@@ -3116,7 +3116,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.84525680541992</v>
+        <v>19.84525489807129</v>
       </c>
       <c r="C110" t="n">
         <v>22.84000015258789</v>
@@ -3145,7 +3145,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>21.85601997375488</v>
+        <v>21.85601425170898</v>
       </c>
       <c r="C111" t="n">
         <v>25.04999923706055</v>
@@ -3174,7 +3174,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.68350410461426</v>
+        <v>19.68350791931152</v>
       </c>
       <c r="C112" t="n">
         <v>22.55999946594238</v>
@@ -3203,7 +3203,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>17.26669120788574</v>
+        <v>17.26670074462891</v>
       </c>
       <c r="C113" t="n">
         <v>19.79000091552734</v>
@@ -3232,7 +3232,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>17.65076637268066</v>
+        <v>17.65077018737793</v>
       </c>
       <c r="C114" t="n">
         <v>20.1299991607666</v>
@@ -3261,7 +3261,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>16.85283851623535</v>
+        <v>16.85284042358398</v>
       </c>
       <c r="C115" t="n">
         <v>19.21999931335449</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>15.22192478179932</v>
+        <v>15.22192001342773</v>
       </c>
       <c r="C116" t="n">
         <v>17.36000061035156</v>
@@ -3319,7 +3319,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>14.19166946411133</v>
+        <v>14.19167423248291</v>
       </c>
       <c r="C117" t="n">
         <v>16.09000015258789</v>
@@ -3348,7 +3348,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.95684623718262</v>
+        <v>12.95684432983398</v>
       </c>
       <c r="C118" t="n">
         <v>14.6899995803833</v>
@@ -3377,7 +3377,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>14.7914457321167</v>
+        <v>14.79144382476807</v>
       </c>
       <c r="C119" t="n">
         <v>16.77000045776367</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>16.64933586120605</v>
+        <v>16.64932632446289</v>
       </c>
       <c r="C120" t="n">
         <v>18.77000045776367</v>
@@ -3435,7 +3435,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>16.56063270568848</v>
+        <v>16.56062698364258</v>
       </c>
       <c r="C121" t="n">
         <v>18.67000007629395</v>
@@ -3464,7 +3464,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>15.6558723449707</v>
+        <v>15.65586948394775</v>
       </c>
       <c r="C122" t="n">
         <v>17.64999961853027</v>
@@ -3493,7 +3493,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>16.82856369018555</v>
+        <v>16.82855606079102</v>
       </c>
       <c r="C123" t="n">
         <v>18.8700008392334</v>
@@ -3551,7 +3551,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>18.25546455383301</v>
+        <v>18.25545883178711</v>
       </c>
       <c r="C125" t="n">
         <v>20.46999931335449</v>
@@ -3580,7 +3580,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>21.87365531921387</v>
+        <v>21.87365341186523</v>
       </c>
       <c r="C126" t="n">
         <v>24.42000007629395</v>
@@ -3609,7 +3609,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>21.47057342529297</v>
+        <v>21.4705753326416</v>
       </c>
       <c r="C127" t="n">
         <v>23.96999931335449</v>
@@ -3638,7 +3638,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>23.54866409301758</v>
+        <v>23.54866600036621</v>
       </c>
       <c r="C128" t="n">
         <v>26.29000091552734</v>
@@ -3667,7 +3667,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>26.82050895690918</v>
+        <v>26.82050704956055</v>
       </c>
       <c r="C129" t="n">
         <v>29.84000015258789</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>27.09913635253906</v>
+        <v>27.0991325378418</v>
       </c>
       <c r="C130" t="n">
         <v>30.14999961853027</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>26.13740730285645</v>
+        <v>26.13740921020508</v>
       </c>
       <c r="C131" t="n">
         <v>29.07999992370605</v>
@@ -3754,7 +3754,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>29.0343074798584</v>
+        <v>29.03431701660156</v>
       </c>
       <c r="C132" t="n">
         <v>32.20000076293945</v>
@@ -3812,7 +3812,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.88276290893555</v>
+        <v>30.88277053833008</v>
       </c>
       <c r="C134" t="n">
         <v>34.25</v>
@@ -3841,7 +3841,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>32.75218200683594</v>
+        <v>32.75219345092773</v>
       </c>
       <c r="C135" t="n">
         <v>36.22000122070312</v>
@@ -3870,7 +3870,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>35.17557907104492</v>
+        <v>35.17560577392578</v>
       </c>
       <c r="C136" t="n">
         <v>38.90000152587891</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.72187805175781</v>
+        <v>36.72187042236328</v>
       </c>
       <c r="C137" t="n">
         <v>40.61000061035156</v>
@@ -3928,7 +3928,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>41.58025741577148</v>
+        <v>41.58028030395508</v>
       </c>
       <c r="C138" t="n">
         <v>45.88000106811523</v>
@@ -3957,7 +3957,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>37.43855285644531</v>
+        <v>37.43856048583984</v>
       </c>
       <c r="C139" t="n">
         <v>41.31000137329102</v>
@@ -3986,7 +3986,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>40.15740585327148</v>
+        <v>40.15741729736328</v>
       </c>
       <c r="C140" t="n">
         <v>44.31000137329102</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>40.98613739013672</v>
+        <v>40.98612976074219</v>
       </c>
       <c r="C141" t="n">
         <v>45.11999893188477</v>
@@ -4044,7 +4044,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>47.31753921508789</v>
+        <v>47.31754302978516</v>
       </c>
       <c r="C142" t="n">
         <v>52.09000015258789</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.25992202758789</v>
+        <v>51.25991439819336</v>
       </c>
       <c r="C143" t="n">
         <v>56.43000030517578</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>48.01689910888672</v>
+        <v>48.01690292358398</v>
       </c>
       <c r="C144" t="n">
         <v>52.77000045776367</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>46.51553726196289</v>
+        <v>46.51551818847656</v>
       </c>
       <c r="C145" t="n">
         <v>51.11999893188477</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>48.7994499206543</v>
+        <v>48.79944229125977</v>
       </c>
       <c r="C146" t="n">
         <v>53.63000106811523</v>
@@ -4218,7 +4218,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>50.69322204589844</v>
+        <v>50.6932258605957</v>
       </c>
       <c r="C148" t="n">
         <v>55.61000061035156</v>
@@ -4247,7 +4247,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>45.27840805053711</v>
+        <v>45.27841186523438</v>
       </c>
       <c r="C149" t="n">
         <v>49.66999816894531</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>46.47523880004883</v>
+        <v>46.47524642944336</v>
       </c>
       <c r="C150" t="n">
         <v>50.77999877929688</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.27435684204102</v>
+        <v>42.27434539794922</v>
       </c>
       <c r="C151" t="n">
         <v>46.18999862670898</v>
@@ -4334,7 +4334,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>44.50749969482422</v>
+        <v>44.50749588012695</v>
       </c>
       <c r="C152" t="n">
         <v>48.63000106811523</v>
@@ -4363,7 +4363,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.55385589599609</v>
+        <v>39.55386352539062</v>
       </c>
       <c r="C153" t="n">
         <v>43.02000045776367</v>
@@ -4392,7 +4392,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>35.53594970703125</v>
+        <v>35.53594589233398</v>
       </c>
       <c r="C154" t="n">
         <v>38.65000152587891</v>
@@ -4421,7 +4421,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.23084259033203</v>
+        <v>30.23084449768066</v>
       </c>
       <c r="C155" t="n">
         <v>32.88000106811523</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>34.46905136108398</v>
+        <v>34.46905899047852</v>
       </c>
       <c r="C156" t="n">
         <v>37.27999877929688</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>30.2713737487793</v>
+        <v>30.27138137817383</v>
       </c>
       <c r="C157" t="n">
         <v>32.7400016784668</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.63045501708984</v>
+        <v>35.63045120239258</v>
       </c>
       <c r="C159" t="n">
         <v>38.34000015258789</v>
@@ -4566,7 +4566,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>36.85717391967773</v>
+        <v>36.857177734375</v>
       </c>
       <c r="C160" t="n">
         <v>39.65999984741211</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>40.95549774169922</v>
+        <v>40.95550918579102</v>
       </c>
       <c r="C161" t="n">
         <v>44.06999969482422</v>
@@ -4624,7 +4624,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>36.13961791992188</v>
+        <v>36.13960647583008</v>
       </c>
       <c r="C162" t="n">
         <v>38.68999862670898</v>
@@ -4653,7 +4653,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.94960784912109</v>
+        <v>41.94958877563477</v>
       </c>
       <c r="C163" t="n">
         <v>44.90999984741211</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.11560821533203</v>
+        <v>46.11560440063477</v>
       </c>
       <c r="C164" t="n">
         <v>49.36999893188477</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>46.82108306884766</v>
+        <v>46.82107925415039</v>
       </c>
       <c r="C166" t="n">
         <v>49.90000152587891</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>50.91205978393555</v>
+        <v>50.91206741333008</v>
       </c>
       <c r="C167" t="n">
         <v>54.2599983215332</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>54.51532363891602</v>
+        <v>54.51531982421875</v>
       </c>
       <c r="C168" t="n">
         <v>57.90000152587891</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>57.47176742553711</v>
+        <v>57.47175979614258</v>
       </c>
       <c r="C169" t="n">
         <v>61.04000091552734</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.60006332397461</v>
+        <v>54.60007095336914</v>
       </c>
       <c r="C170" t="n">
         <v>57.9900016784668</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>54.89491271972656</v>
+        <v>54.8948974609375</v>
       </c>
       <c r="C171" t="n">
         <v>58.11999893188477</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.92324447631836</v>
+        <v>46.92324829101562</v>
       </c>
       <c r="C173" t="n">
         <v>49.68000030517578</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>57.32295989990234</v>
+        <v>57.32296752929688</v>
       </c>
       <c r="C175" t="n">
         <v>60.45000076293945</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>61.00225448608398</v>
+        <v>61.00224304199219</v>
       </c>
       <c r="C176" t="n">
         <v>64.33000183105469</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>58.60757446289062</v>
+        <v>58.60755920410156</v>
       </c>
       <c r="C177" t="n">
         <v>61.59999847412109</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>56.35269546508789</v>
+        <v>56.35269927978516</v>
       </c>
       <c r="C179" t="n">
         <v>59.22999954223633</v>
@@ -5146,7 +5146,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>78.7060546875</v>
+        <v>78.70608520507812</v>
       </c>
       <c r="C180" t="n">
         <v>82.48000335693359</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>82.35129547119141</v>
+        <v>82.35130310058594</v>
       </c>
       <c r="C181" t="n">
         <v>86.30000305175781</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>92.25633239746094</v>
+        <v>92.25634765625</v>
       </c>
       <c r="C182" t="n">
         <v>96.68000030517578</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>127.7290191650391</v>
+        <v>127.7290115356445</v>
       </c>
       <c r="C184" t="n">
         <v>133.6000061035156</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>126.8781127929688</v>
+        <v>126.8781204223633</v>
       </c>
       <c r="C185" t="n">
         <v>132.7100067138672</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>132.2908630371094</v>
+        <v>132.2908325195312</v>
       </c>
       <c r="C186" t="n">
         <v>138.1300048828125</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>134.0147247314453</v>
+        <v>134.0147399902344</v>
       </c>
       <c r="C188" t="n">
         <v>139.9299926757812</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>129.6544189453125</v>
+        <v>129.6543884277344</v>
       </c>
       <c r="C189" t="n">
         <v>135.1300048828125</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>131.11279296875</v>
+        <v>131.1128082275391</v>
       </c>
       <c r="C191" t="n">
         <v>136.6499938964844</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>141.4536895751953</v>
+        <v>141.4536743164062</v>
       </c>
       <c r="C192" t="n">
         <v>147.1900024414062</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>151.2273559570312</v>
+        <v>151.2273254394531</v>
       </c>
       <c r="C193" t="n">
         <v>157.3600006103516</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>126.8918380737305</v>
+        <v>126.891845703125</v>
       </c>
       <c r="C196" t="n">
         <v>131.8000030517578</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>106.2406311035156</v>
+        <v>106.2406234741211</v>
       </c>
       <c r="C197" t="n">
         <v>110.3499984741211</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>87.80615234375</v>
+        <v>87.80611419677734</v>
       </c>
       <c r="C199" t="n">
         <v>90.98000335693359</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>102.2828674316406</v>
+        <v>102.2828598022461</v>
       </c>
       <c r="C200" t="n">
         <v>105.9800033569336</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>91.02052307128906</v>
+        <v>91.02051544189453</v>
       </c>
       <c r="C201" t="n">
         <v>94.06999969482422</v>
@@ -5784,7 +5784,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>79.27407073974609</v>
+        <v>79.27405548095703</v>
       </c>
       <c r="C202" t="n">
         <v>81.93000030517578</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>106.3052978515625</v>
+        <v>106.305290222168</v>
       </c>
       <c r="C204" t="n">
         <v>109.5999984741211</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>108.1384811401367</v>
+        <v>108.1384582519531</v>
       </c>
       <c r="C206" t="n">
         <v>111.4899978637695</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>109.8889236450195</v>
+        <v>109.8889312744141</v>
       </c>
       <c r="C209" t="n">
         <v>113.0299987792969</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>129.9296264648438</v>
+        <v>129.9296112060547</v>
       </c>
       <c r="C210" t="n">
         <v>133.3000030517578</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>147.7571716308594</v>
+        <v>147.7571868896484</v>
       </c>
       <c r="C212" t="n">
         <v>151.5899963378906</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>149.2205657958984</v>
+        <v>149.2205505371094</v>
       </c>
       <c r="C213" t="n">
         <v>152.7599945068359</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>135.2421264648438</v>
+        <v>135.2420959472656</v>
       </c>
       <c r="C214" t="n">
         <v>138.4499969482422</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>129.2834625244141</v>
+        <v>129.2834930419922</v>
       </c>
       <c r="C215" t="n">
         <v>132.3500061035156</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>146.6239471435547</v>
+        <v>146.6239776611328</v>
       </c>
       <c r="C216" t="n">
         <v>149.7799987792969</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>160.8380432128906</v>
+        <v>160.8380279541016</v>
       </c>
       <c r="C218" t="n">
         <v>164.3000030517578</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>197.7061309814453</v>
+        <v>197.7061157226562</v>
       </c>
       <c r="C219" t="n">
         <v>201.6199951171875</v>
@@ -6306,7 +6306,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>202.2266540527344</v>
+        <v>202.2266387939453</v>
       </c>
       <c r="C220" t="n">
         <v>206.2299957275391</v>
@@ -6364,7 +6364,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>211.2893676757812</v>
+        <v>211.2893524169922</v>
       </c>
       <c r="C222" t="n">
         <v>215.0800018310547</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>231.8308563232422</v>
+        <v>231.8308410644531</v>
       </c>
       <c r="C223" t="n">
         <v>235.9900054931641</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>208.4601135253906</v>
+        <v>208.4601440429688</v>
       </c>
       <c r="C224" t="n">
         <v>212.1999969482422</v>
@@ -6451,7 +6451,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>194.1548309326172</v>
+        <v>194.1548004150391</v>
       </c>
       <c r="C225" t="n">
         <v>197.2599945068359</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>198.8694152832031</v>
+        <v>198.8694000244141</v>
       </c>
       <c r="C226" t="n">
         <v>202.0500030517578</v>
@@ -6509,7 +6509,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>178.7216186523438</v>
+        <v>178.7216339111328</v>
       </c>
       <c r="C227" t="n">
         <v>181.5800018310547</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>172.3641967773438</v>
+        <v>172.3641815185547</v>
       </c>
       <c r="C228" t="n">
         <v>174.7100067138672</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>160.4463806152344</v>
+        <v>160.4463653564453</v>
       </c>
       <c r="C229" t="n">
         <v>162.6300048828125</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>177.928466796875</v>
+        <v>177.9284515380859</v>
       </c>
       <c r="C230" t="n">
         <v>180.3500061035156</v>
@@ -6625,7 +6625,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>156.3068084716797</v>
+        <v>156.3068237304688</v>
       </c>
       <c r="C231" t="n">
         <v>158.0700073242188</v>
@@ -6654,7 +6654,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>143.5012512207031</v>
+        <v>143.5012359619141</v>
       </c>
       <c r="C232" t="n">
         <v>145.1199951171875</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>149.0289001464844</v>
+        <v>149.0288848876953</v>
       </c>
       <c r="C233" t="n">
         <v>150.7100067138672</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>155.4422912597656</v>
+        <v>155.4422607421875</v>
       </c>
       <c r="C234" t="n">
         <v>156.75</v>
@@ -6857,7 +6857,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>231.8177947998047</v>
+        <v>231.8178100585938</v>
       </c>
       <c r="C239" t="n">
         <v>233.1000061035156</v>
